--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128651997</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128651997</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128651997</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128651997</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7998-2025 artfynd.xlsx
+++ b/artfynd/A 7998-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>128651997</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -780,7 +780,7 @@
         <v>128651998</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
